--- a/Payer Routing/AZ_Blue_Prefix_Routing_2026-09-15.xlsx
+++ b/Payer Routing/AZ_Blue_Prefix_Routing_2026-09-15.xlsx
@@ -10,11 +10,12 @@
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="64772 Determinations" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Routing by Prefix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Code List Findings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Contacts" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'64772 Determinations'!$A$4:$G$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Routing by Prefix'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'64772 Determinations'!$A$4:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Routing by Prefix'!$A$4:$H$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -124,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,6 +163,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -529,10 +533,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="112" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -546,251 +550,222 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>v2 - 15 September 2026. Updated with the billing department's live lookup results.</t>
+          <t>v3 - 15 September 2026. Verified against the AZ Blue Prior Authorization Requirements Code Lists (updated 09/01/2026).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>THE HEADLINE FINDING</t>
+          <t>*** TWO RULES THAT CHANGE THE STAKES ***</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>On an M2K member, AZ Blue's lookup tool returned 'no authorization required' for CPT 64772.</t>
+          <t>1. NO AUTH = NO PAYMENT, AND YOU CANNOT BILL THE MEMBER.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>For a member delegated to AZPC, that answer is WRONG - AZPC does require authorization.</t>
+          <t xml:space="preserve">   AZ Blue: "For dates of service on and after July 1, 2026, when a required prior auth is not</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   obtained, the claim (or claim line) for that service will not be reimbursed. AZ Blue network</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>The tool says so itself. Its note reads: 'IMPORTANT! This response is valid only for Medicare</t>
+          <t xml:space="preserve">   providers may not bill the member for the service."</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Advantage plans administered by AZ Blue. Check the back of the ID card for the plan's prior auth</t>
+          <t xml:space="preserve">   A missed AZPC authorization on CPT 64772 is therefore a total write-off.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>and claim administrator.'</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2. THE AZ BLUE LOOKUP TOOL IS NOT DELEGATION-AWARE, AND SAYS SO.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>So the AZ Blue lookup tool is NOT delegation-aware. On any M2K member you must identify the</t>
+          <t xml:space="preserve">   Its result note: "IMPORTANT! This response is valid only for Medicare Advantage plans</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>vendor FIRST - AZ Blue retained, OHNAZ (Optum), or AZPC - and then check that vendor's own list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Why this workbook exists</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>'BCBS AZ' is not one payer. AZ Blue runs nine published plan families, each with its own vendor,</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>code list and phone number. Route by ALPHA PREFIX and PAYER ID, never by the name on the card.</t>
+          <t xml:space="preserve">   administered by AZ Blue. Check the back of the ID card for the plan’s prior auth and claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   administrator."  On M2K it returns "not required" for 64772 - right for AZ Blue and OHNAZ,</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   WRONG for AZPC, which does require authorization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Absence from a list is not an absolute guarantee</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>AZ Blue reserves the right: "AZ Blue reserves the right to require prior authorization for such</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>newly released and changed items even though the lists have not yet been updated to include them."</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Questions on a specific code: 602-864-4320 or 1-800-232-2345.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>How to use it</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>1. Read the prefix from the member ID.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2. For M2K, identify the VENDOR before trusting any answer (see the headline above).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>3. Go to the '64772 Determinations' tab for the answer we have already established.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>4. Use 'Routing by Prefix' for any other code, then verify with that entity's own list.</t>
+          <t>1. Read the prefix from the member ID and find it on 'Routing by Prefix'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2. For M2K, identify the VENDOR from the ID card before trusting any answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>3. Go to '64772 Determinations' for the answers already established.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Prefixes confirmed by the billing department</t>
-        </is>
-      </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>IAZ    = ACA StandardHealth with Health Choice  (ACA marketplace - commercial risk)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>MZHHC  = Health Choice Pathway Medicare Advantage  (D-SNP)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>HCI    = Health Choice 'Acute' Medicaid  (prefix HCI followed by the AHCCCS ID; appears as HCIA in our system)</t>
+          <t>4. 'Code List Findings' records what the AZ Blue code-list workbook itself says about 64772.</t>
         </is>
       </c>
     </row>
     <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Verification convention</t>
+        </is>
+      </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>M2K    = AZ Blue Medicare Advantage</t>
+          <t>Published         = stated in AZ Blue's own code-list workbook or on a published page.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>R      = Federal Employee Program (FEP)</t>
+          <t>Practice-verified = our billing department ran the payer's tool or list and recorded the result.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>XBS    = Medicare Supplement / Medigap</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>AOZ, AZI, AZK, IVR = Strategic Hub plans</t>
+          <t>To confirm        = no source found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Timely filing</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>AZ Blue's initial filing limit dropped from 365 days to 90 DAYS for dates of service on or after</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Verification convention</t>
-        </is>
-      </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Practice-verified = our billing department ran the payer's own tool or list and recorded the result.</t>
+          <t>1 January 2026. Optum is also 90 days. Health Choice lines run 6-7 months (12 months</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Published         = stated on a payer published page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>To confirm        = no source found; must be confirmed before it is relied on.</t>
+          <t>non-contracted on the ACA line). Misrouting is no longer absorbed by a long window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Still open</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Optum's UHC-MEMBER prior-auth list (a different document from the BCBS-member one).</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Timely filing - why misrouting is expensive</t>
-        </is>
-      </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>AZ Blue's initial filing limit dropped from 365 days to 90 DAYS for dates of service on or after</t>
+          <t>Whether one authorization covers BOTH the facility (UB-04) and professional (CMS-1500) claim,</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>1 January 2026. Optum is also 90 days. Health Choice lines run 6-7 months (12 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>non-contracted on the ACA line). Time lost routing to the wrong entity is no longer absorbed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Still open</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>AZ Blue Prior Authorization Code List - to be folded in when the file is supplied.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Whether one authorization covers BOTH the facility (UB-04) and professional (CMS-1500) claim,</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  or whether the ASC needs its own, and whether the auth is tied to a TIN/NPI or a place of service.</t>
+          <t xml:space="preserve">  whether it is tied to a TIN/NPI, and whether it names a place of service.</t>
         </is>
       </c>
     </row>
@@ -805,16 +780,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,7 +802,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Transection or avulsion of other spinal nerve, extradural.  Green = no auth required.  Red = auth REQUIRED.</t>
+          <t>Transection or avulsion of other spinal nerve, extradural.   Green = no auth.  Red = AUTH REQUIRED.</t>
         </is>
       </c>
     </row>
@@ -859,7 +834,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Source / Document</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -868,471 +843,601 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
+          <t>(none of the below)</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue commercial (Standard)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue + eviCore</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>64772 is not on the 2026 STANDARD Code List (1,909 rows). eviCore's MSK/interventional pain program is MA-only, so no eviCore pathway exists either.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Requirements Code Lists, 2026 STANDARD Code List tab</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>(none of the below)</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>State of Arizona Group</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue + eviCore</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>64772 not on the list</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>2026 State of AZ Grp List tab</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>(none of the below)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Teamsters / Snell &amp; Wilmer groups</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>64772 not on either list</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>2026 Teamsters and Snell &amp; Wilmer tabs</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
           <t>M2K</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>AZ Blue Medicare Advantage</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>AZ Blue (retained)</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>AZ Blue Prior Authorization Lookup returned 'not required'</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>AZ Blue PA Lookup tool</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Not on the 2026 Medicare Advantage List; AZ Blue PA Lookup also returned 'not required'</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>2026 Medicare Advantage List tab; AZ Blue PA Lookup</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Published + practice-verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>M2K</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue Medicare Advantage</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>OHNAZ (Optum)</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>64772 not listed in the Optum prior-auth requirements article</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Practice-verified</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>M2K</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>AZ Blue Medicare Advantage</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>OHNAZ (Optum)</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>AZPC (Arizona Priority Care)</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>YES - AUTH REQUIRED</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>64772 is NOT on the 'services that do NOT require authorization' grid. Inverted list: absence means auth IS required.</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>AZPC-2026-Services-That-Do-Not-Require-Authorization, Attachment A, eff. 8.21.2026 (AZ CONNECT)</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Practice-verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Federal Employee Program (FEP)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue FEP unit</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>64772 not listed in the Optum prior-auth requirements article</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>2026 OptumCare Network of Arizona: Blue Cross Blue Shield prior authorization requirements</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Not on the 2026 FEP List or the FEP Blue Focus list; confirmed twice by AZ Blue PA Lookup and Availity</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>2026 FEP List and FEPBluefocusList tabs; AZ Blue PA Lookup; Availity</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Published + practice-verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>XBS</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Medicare Supplement / Medigap</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>CMS - follows the Medicare determination</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>No auth required on Medigap plans</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue PA Lookup</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Practice-verified</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>M2K</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>AZ Blue Medicare Advantage</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>AZPC (Arizona Priority Care)</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>YES - AUTH REQUIRED</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>64772 is NOT on the 'services that do NOT require authorization' grid. Inverted list: absence means auth IS required.</t>
-        </is>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>AZPC-2026-Services-That-Do-Not-Require-Authorization_Attachment-A_Effective-8.21.2026_AZ-CONNECT</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>IAZ</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ACA StandardHealth with Health Choice</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Health Choice team</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Not on the ACA StandardHealth PA grid; an auth was filed and none was required</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>ACA StandardHealth PA Grid; Health Choice portal</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Practice-verified</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Federal Employee Program (FEP)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>AZ Blue FEP unit</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>MZH / MZHHC</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Health Choice Pathway Medicare Advantage (D-SNP)</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Health Choice team</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Confirmed twice - AZ Blue PA Lookup and the Availity authorization request tool both returned 'not required'</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>AZ Blue PA Lookup; Availity Essentials</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>An auth was filed and none was required</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Health Choice portal</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Practice-verified</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>XBS</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Medicare Supplement / Medigap</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>CMS - follows the Medicare determination</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>HCI (+ AHCCCS ID)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Health Choice 'Acute' Medicaid (AHCCCS)</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Health Choice team</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>No auth required on Medigap plans</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>AZ Blue PA Lookup</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>An auth was filed and none was required</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Health Choice portal</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>Practice-verified</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>IAZ</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>ACA StandardHealth with Health Choice</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Health Choice team</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>64772 not listed on the PA grid; an auth was filed and none was required</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>ACA StandardHealth with Health Choice Prior Authorization Grid</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Practice-verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>MZHHC</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Health Choice Pathway Medicare Advantage (D-SNP)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Health Choice team</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>An auth was filed and none was required</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Health Choice provider portal</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Practice-verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>HCI (+ AHCCCS ID)</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Health Choice 'Acute' Medicaid (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Health Choice team</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>An auth was filed and none was required</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Health Choice provider portal</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>Practice-verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>(none of the below)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>AZ Blue commercial</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>AZ Blue + eviCore</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>AOZ, AZI, AZK, IVR</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Strategic Hub plans</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>BCBS South Carolina</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>TO CONFIRM</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>eviCore's MSK / interventional pain program is Medicare Advantage ONLY, so no eviCore precert pathway exists. AZ Blue's own requirement not yet checked.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>BCBSAZ MSK code list eff. 01/01/2026 (64772 absent; zero 647xx codes)</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>A Blue Plan partner handles UM for these plans - not checked</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Call 800-868-1032</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>AOZ, AZI, AZK, IVR</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Strategic Hub plans</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>A partner Blue plan</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>JAR, JAZ, JCG, JGF, JKS,
+JPZ, JSW, K8Y, K8Z,
+MKQ, NBT, PTP</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Jointly Administered plans (incl. AmeriBen)</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>A TPA - check ID card</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>TO CONFIRM</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Not checked - a partner Blue plan administers these</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>BCBS SC 'My Insurance Manager'</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>UM handled by a TPA. The SPD governs the benefit; the TPA's criteria set (MCG / Carelon / network policies) governs medical necessity.</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue Introduction tab, EXCEPTIONS</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>(no prefix)</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>CHS group plans</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>A TPA - call the number on the ID card</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>CHS groups use a TPA for prior authorization and medical policy</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>AZ Blue Introduction tab, EXCEPTIONS</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>To confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>(out-of-state)</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>BlueCard</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>The member's HOME Blue plan</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>VARIES BY HOME PLAN</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Each home plan sets its own rules</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>BlueCard Medical Policy Router</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>To confirm</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>(TPA on card)</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>CHS group / TPA jointly administered</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>The group's TPA</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>VARIES BY GROUP</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Self-funded - the SPD governs the benefit</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>TPA contact list / the group's SPD</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>To confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>'No authorization required' is NOT the same as 'covered'. No payer publishes medical-necessity criteria for 64772; every claim is decided on the operative report. Attach it to the first claim, unprompted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>On Medicare Advantage and D-SNP lines, AZ Blue policy applies CMS NCDs/LCDs first - for 64772 that is NCD 160.1, which covers 'surgical cutting of the nerve (rhizolysis)' but defers to medical review case by case.</t>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>'No authorization required' is NOT 'covered'. No payer publishes medical-necessity criteria for 64772 - every claim is decided on the operative report. Attach it to the first claim, unprompted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>AZ Blue has NO medical policy for 64772 (its 'Current Med Pol Available' tab flags the code NO). Its sibling codes 63185, 63190 and 64740 are flagged NO as well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>64772 IS flagged ON for commercial MEDICAL REVIEW in AZ Blue's CommercialMR tab - consistent with no prior auth but post-service scrutiny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>On Medicare Advantage and D-SNP lines, CMS NCDs/LCDs govern - for 64772 that is NCD 160.1.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G16"/>
+  <autoFilter ref="A4:G19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1343,582 +1448,535 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="66" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AZ Blue - who handles utilisation management, by member ID prefix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source: AZ Blue Prior Authorization Requirements Code Lists, updated 09/01/2026.  Prefix assignments below are quoted from its EXCEPTIONS section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Alpha Prefix</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Plan Family</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Line of Business</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Who Decides Auth</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Submit Via</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Coverage Criteria Source</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="72" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+    </row>
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>(none of the below)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>AZ Blue Plans</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>AZ Blue Plans - Standard</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Commercial (group &amp; individual)</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>AZ Blue + eviCore</t>
         </is>
       </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>Availity Essentials; eviCore; fax/online forms</t>
-        </is>
-      </c>
-      <c r="F2" s="15" t="inlineStr">
-        <is>
-          <t>602-864-4320 (UM, 24/7)</t>
-        </is>
-      </c>
-      <c r="G2" s="15" t="inlineStr">
-        <is>
-          <t>AZ Blue proprietary policies; MCG; eviCore guidelines</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="inlineStr">
-        <is>
-          <t>eviCore's MSK / interventional pain program is MEDICARE ADVANTAGE ONLY. No eviCore precert pathway here, so no pre-service approval to obtain.</t>
-        </is>
-      </c>
-      <c r="I2" s="15" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="72" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>602-864-4320 (UM 24/7) / 1-800-232-2345</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Availity Essentials; eviCore</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>AZ Blue medical policies; MCG; eviCore guidelines</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>eviCore's MSK/interventional pain program is MEDICARE ADVANTAGE ONLY. Also: some employer groups on standard requirements are NOT delegated to eviCore - check eligibility &amp; benefits, service type 30, under 'Network Unknown'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>IAZ</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>ACA StandardHealth with Health Choice</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>ACA marketplace (COMMERCIAL risk)</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Health Choice team</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>800-322-8670</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>providerportal.healthchoiceaz.com</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>1-800-322-8670 (Maricopa 480-968-6866)</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Clinical guidelines; eviCore for RADIOLOGY / CARDIAC IMAGING ONLY</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Payer ID RP105. Commercial risk but Health Choice administration - does NOT route through the AZ Blue commercial lane.</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>MZHHC</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Payer ID RP105. Commercial risk, Health Choice administration - does NOT route through the AZ Blue commercial lane. PA fax 602-864-5308.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>MZH  (seen as MZHHC)</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Health Choice Pathway Medicare Advantage</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>D-SNP (Medicare + Medicaid)</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Health Choice team</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>800-322-8670 / PA 1-800-656-8991</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Secure provider portal</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>1-800-656-8991</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>InterQual; UpToDate; CMS NCDs / LCDs; NCCN</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>D-SNP, so NCDs/LCDs govern - for 64772 that means NCD 160.1.</t>
-        </is>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>Practice-verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>HCI (+ AHCCCS ID)</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>InterQual; UpToDate; CMS NCDs/LCDs; NCCN</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>D-SNP, so NCDs/LCDs govern - for 64772 that is NCD 160.1. PA fax 1-877-424-5680.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>HCI  (+ AHCCCS ID; seen as HCIA)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Health Choice 'Acute' Medicaid</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>AHCCCS Medicaid</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Health Choice team</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>800-322-8670</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>providerportal.healthchoiceaz.com</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>1-800-322-8670</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Clinical guidelines; AHCCCS AMPM</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>Payer ID 62179. Appears as HCIA in our system. Many items on the abbreviated PA list are NOTIFICATION ONLY - ask rather than assume.</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>Practice-verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Payer ID 62179. Many items on the abbreviated PA list are NOTIFICATION ONLY - ask rather than assume. PA fax 1-877-422-8120.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Federal Employee Program (FEP)</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Commercial (federal)</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>AZ Blue FEP unit + Caremark (pharmacy)</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>AZ Blue FEP unit + Caremark</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>602-864-4102 / 1-800-345-7562</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Availity Essentials</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>602-864-4102 / 1-800-345-7562</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>FEP Service Benefit Plan brochure; FEP medical policies; FEP utilization guidelines</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>FEP runs its OWN policy set - AZ Blue proprietary policies do NOT govern. Confirm the member's option (Standard / Basic / Blue Focus). FEP's term is 'prior approval'.</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>FEP brochure; FEP medical policies; FEP utilization guidelines</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>FEP runs its OWN policy set - AZ Blue policies do NOT govern. Confirm the option (Standard / Basic / Blue Focus). FEP's term is 'prior approval'. FEP requires precert for ALL non-emergency admissions except routine maternity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>M2K</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Medicare Advantage</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Medicare Advantage</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>THREE vendors: AZ Blue retained / OHNAZ (Optum) / AZPC</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>Availity; eviCore; fax form; OHNAZ or AZPC portals</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>THREE vendors - AZ Blue, OHNAZ (Optum), or AZPC. CHECK ID CARD.</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>AZ Blue 1-800-446-8331 | OHNAZ 1-877-370-2845 | AZPC 480-499-8720</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Availity; eviCore; OHNAZ or AZPC portals</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>CMS NCDs and LCDs FIRST; then eviCore; MCG</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>IDENTIFY THE VENDOR FIRST. The AZ Blue lookup tool answers only for plans AZ BLUE administers - its own note says so. AZPC requires auth for 64772 where AZ Blue and Optum do not.</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>IDENTIFY THE VENDOR FIRST. The AZ Blue lookup tool answers only for AZ Blue-administered plans. AZPC REQUIRES auth for 64772 where AZ Blue and Optum do not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>AOZ, AZI, AZK, IVR</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Strategic Hub Plans</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Strategic Hub plans</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>A partner Blue plan</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>A Blue Plan partner - BCBS South Carolina</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>800-868-1032</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>BCBS SC 'My Insurance Manager'</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>(per partner plan)</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>Strategic Hub medical policies</t>
         </is>
       </c>
-      <c r="H8" s="15" t="inlineStr"/>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr"/>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>XBS</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Medicare Supplement / Medigap</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Medicare Supplement</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>CMS - follows the Medicare determination</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>(n/a)</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>(n/a)</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>CMS coverage rules (NCD / LCD)</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>Get it right with Noridian and the supplement follows. AZ Blue determines only foreign-travel emergencies.</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Get it right with Noridian and the supplement follows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>JAR, JAZ, JCG, JGF, JKS, JPZ, JSW, K8Y, K8Z, MKQ, NBT, PTP</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Jointly Administered plans (incl. AmeriBen)</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Commercial self-funded</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>A TPA - CHECK ID CARD</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>(number on ID card)</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Per the TPA</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>The TPA's criteria set - e.g. MCG, Carelon, or a network's medical policies</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Self-funded: the SPD outranks every guideline set. AmeriBen's precertification LETTER names the guideline it applied - use that rather than guessing between MCG / HealthLink / Carelon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>(no prefix)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>CHS group plans</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Commercial self-funded</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>A TPA</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>(number on ID card)</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Per the TPA</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>The TPA's own policies</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>CHS groups use a TPA for prior authorization AND medical policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>(out-of-state member)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>BlueCard</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Varies by home plan</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>The member's HOME Blue plan</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
-        <is>
-          <t>Availity BlueCard authorization request</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>(per home plan)</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Availity BlueCard request</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>BlueCard Medical Policy Router - enter the prefix</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>Every home plan has its own position. Check PER MEMBER.</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>(TPA named on card)</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Corporate Health Services (CHS) group plans</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Commercial self-funded</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>The group's TPA</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Number on the back of the card</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>(per TPA)</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>The TPA's own policies</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>Self-funded: the plan document (SPD) governs the benefit.</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>(TPA named on card)</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>AZ Blue &amp; TPA jointly administered plans</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Commercial self-funded</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>Split AZ Blue / TPA - VARIES BY GROUP</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Per the 2026 TPA contact list</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>(per TPA)</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>The TPA's own policies</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>Confirm WHICH half of the administration owns utilisation review for that group.</t>
-        </is>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A4:H15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1929,20 +1987,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>What the AZ Blue code-list workbook says about CPT 64772</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source: AZ Blue Prior Authorization Requirements Code Lists, updated 09/01/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tab checked</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>64772 present?</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>What it means</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>2026 STANDARD Code List</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>1,909</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>No prior auth for AZ Blue commercial / standard groups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2026 State of AZ Grp List</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>1,973</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>No prior auth for the State of Arizona group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>2026 Teamsters Group List</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>No prior auth for the Teamsters group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026 FEP List</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>2,219</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>No prior approval for FEP - matches the Availity and lookup-tool results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>FEPBluefocusList</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>1,849</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>No prior approval under FEP Blue Focus either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2026 Medicare Advantage List</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>2,117</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>No prior auth for AZ BLUE-ADMINISTERED Medicare Advantage. Does NOT speak for OHNAZ or AZPC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Snell &amp; Wilmer Group List</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>No prior auth for that group.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MasterCodifiedPrecertList</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Not on the master precert list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>FEP MR / MAMR</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>1,182 / 711</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Not flagged for FEP or Medicare Advantage medical review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Current Med Pol Available</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>NO (flag = NO)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>AZ BLUE HAS NO MEDICAL POLICY FOR 64772. Siblings 63185, 63190 and 64740 are flagged NO as well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>CommercialMR</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>2,554</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>YES - flagged ON</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>64772 IS flagged for COMMERCIAL MEDICAL REVIEW. No prior auth, but expect post-service scrutiny - send the operative report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>M300 (historical config)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>7,695</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Category 'Ambulatory Surgery'. 2019 Precert List = OFF, 2020 Precert List = ON, Medicare = ON, ACA = ON. AZ Blue has had this code on a precert list before, so re-check the list each year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Denied2019</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>7,404</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>20 denied claims for 64772 in 2019 - this code has a denial history at AZ Blue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>PreCert Detail</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>2,350</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>No precert decision history, consistent with it not being on a current precert list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Bottom line</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>64772 is absent from ALL TEN plan-facing prior-auth lists in a workbook updated 09/01/2026. AZ Blue itself requires no prior authorization for it on any line. The only AZ Blue entity that does is AZPC, whose list is published separately and inverted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Caveat: AZ Blue reserves the right to require prior authorization for newly released or changed items not yet on the lists. Re-check annually and call 602-864-4320 with questions on a specific code.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="64" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AZ Blue, Health Choice, Optum and AZPC - contacts and key documents</t>
+          <t>Contacts and key documents</t>
         </is>
       </c>
     </row>
@@ -1976,45 +2417,49 @@
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>AZ Blue - general</t>
+          <t>AZ Blue - UM (commercial)</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>General inquiries</t>
+          <t>Utilisation management, 24/7 clinical</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>1-844-995-2583</t>
+          <t>602-864-4320 / 1-800-232-2345</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>azblue.com</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr"/>
+          <t>UtilMgmt@azblue.com</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Also the number for questions on a specific code</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>AZ Blue - UM (commercial)</t>
+          <t>AZ Blue - general</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Utilisation management, 24/7 clinical</t>
+          <t>General inquiries</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>602-864-4320</t>
+          <t>1-844-995-2583</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>UtilMgmt@azblue.com</t>
+          <t>azblue.com</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr"/>
@@ -2022,17 +2467,17 @@
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>AZ Blue - provider services</t>
+          <t>AZ Blue - Medicare Advantage</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Provider services</t>
+          <t>MA utilisation management</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>1-800-322-8670</t>
+          <t>1-800-446-8331</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr"/>
@@ -2041,96 +2486,96 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>AZ Blue - Medicare Advantage</t>
+          <t>AZ Blue - FEP unit</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>MA utilisation management</t>
+          <t>FEP prior approval</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>1-800-446-8331</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
+          <t>602-864-4102 / 1-800-345-7562</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Availity Essentials</t>
+        </is>
+      </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Ask which entity adjudicates a code absent from the eviCore list</t>
+          <t>Pharmacy 1-877-727-3784</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>AZ Blue - FEP unit</t>
+          <t>AZ Blue - PA lookup tool</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>FEP prior approval</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>602-864-4102 / 1-800-345-7562</t>
-        </is>
-      </c>
+          <t>Check a code for a member</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr"/>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Availity Essentials</t>
+          <t>azblue.com/lookup</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>FEP pharmacy 1-877-727-3784</t>
+          <t>Needs a live Member ID + DOS. ANSWERS ONLY FOR PLANS AZ BLUE ADMINISTERS.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>AZ Blue - PA lookup tool</t>
+          <t>AZ Blue - PA code lists</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Check a code for a member</t>
+          <t>The source workbook, updated 09/01/2026</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>azblue.com/prior-authorization-lookup/providers</t>
+          <t>azblue.com/priorauth</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Needs a live Member ID + DOS. ANSWERS ONLY FOR PLANS AZ BLUE ADMINISTERS - not for delegated members.</t>
+          <t>Ten plan-facing tabs; 64772 on none of them</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>AZ Blue - PA code lists</t>
+          <t>AZ Blue - eviCore resources</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Code list workbook, eff. April 2026</t>
+          <t>Current eviCore code lists and guidelines</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr"/>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>assets.azblue.com/asset/1b2ef17e-2036-48a4-b0d7-cb49806d433a/AZ-BluePriorAuth-CodeListsEffective202604.xlsx</t>
+          <t>azblue.com/auth</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Tabs by plan family, incl. FEP and MA tabs</t>
+          <t>To test eviCore delegation: eligibility &amp; benefits, service type 30, look under 'Network Unknown'</t>
         </is>
       </c>
     </row>
@@ -2142,12 +2587,12 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Provider portal</t>
+          <t>Prefixes IAZ, HCI, MZH</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>1-800-322-8670</t>
+          <t>800-322-8670</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -2157,36 +2602,32 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>ACA fax 602-864-5308 | Medicaid fax 1-877-422-8120 | Pathway fax 1-877-424-5680</t>
+          <t>ACA fax 602-864-5308 | Medicaid fax 1-877-422-8120 | Pathway PA 1-800-656-8991, fax 1-877-424-5680</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Health Choice Pathway</t>
+          <t>BCBS South Carolina</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>D-SNP prior authorization</t>
+          <t>Strategic Hub plans (AOZ, AZI, AZK, IVR)</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>1-800-656-8991</t>
+          <t>800-868-1032</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Secure provider portal</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Rx fax 1-877-424-5690</t>
-        </is>
-      </c>
+          <t>My Insurance Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -2234,80 +2675,57 @@
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>64772 NOT listed - no auth required. SEPARATE from the UHC list.</t>
+          <t>64772 NOT listed - no auth. SEPARATE from the UHC-member list, which is still unchecked.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Optum - UHC member PA list</t>
+          <t>Arizona Priority Care (AZPC)</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>For UHC members delegated to Optum</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr"/>
+          <t>Delegated UM for some M2K members</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>480-499-8720</t>
+        </is>
+      </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>business.optum.com/content/dam/noindex-resources/consumers/pdfs/forms/prior-authorization-requirements-arizona-uhc.pdf</t>
+          <t>AZ Connect: azconnect.azprioritycare.com/production/default.asp</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Doc ref OHNC-1-24-00647. Not interchangeable with the BCBS list.</t>
+          <t>INVERTED LIST - publishes what does NOT require auth. Absence = auth IS required.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Arizona Priority Care (AZPC)</t>
+          <t>AZPC - no-auth grid</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Delegated UM for some M2K members</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>480-499-8720</t>
-        </is>
-      </c>
+          <t>Services that do NOT require authorization</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr"/>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>AZ Connect: azconnect.azprioritycare.com/production/default.asp</t>
+          <t>AZPC-2026-Services-That-Do-Not-Require-Authorization, Attachment A, eff. 8.21.2026</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>INVERTED LIST - publishes services that do NOT require auth. Absence = auth IS required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>AZPC - no-auth grid</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Services that do NOT require authorization</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>AZPC-2026-Services-That-Do-Not-Require-Authorization_Attachment-A_Effective-8.21.2026_AZ-CONNECT</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>64772 NOT on the grid, therefore AUTH IS REQUIRED for M2K members delegated to AZPC.</t>
+          <t>64772 NOT on the grid - AUTH IS REQUIRED for M2K members delegated to AZPC.</t>
         </is>
       </c>
     </row>

--- a/Payer Routing/AZ_Blue_Prefix_Routing_2026-09-15.xlsx
+++ b/Payer Routing/AZ_Blue_Prefix_Routing_2026-09-15.xlsx
@@ -10,8 +10,10 @@
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="64772 Determinations" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Routing by Prefix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Code List Findings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Contacts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vendor Notes" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Facility + Professional" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Code List Findings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Contacts" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'64772 Determinations'!$A$4:$G$19</definedName>
@@ -1987,6 +1989,469 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="84" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Vendor mechanics - how each one's list actually works</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The same 'not on the list' result means different things at different vendors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Vendor / tool</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>How its list works</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>AZ Blue code lists</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Lists what DOES require prior auth.</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Not on the list = no prior auth.</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>64772 absent from all ten plan-facing tabs. But AZ Blue reserves the right to require PA for items not yet listed - call 602-864-4320.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>AZ Blue PA lookup tool</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Member-specific; needs a live Member ID + date of service.</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Use it, but ONLY trust it for plans AZ Blue administers.</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>NOT delegation-aware. Its own note says the response is valid only for MA plans administered by AZ Blue - check the ID card for the real administrator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="68" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Optum (OHNAZ)</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Lists what DOES require prior auth. SEPARATE documents per health plan.</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Use the BCBS-member list for a BCBS member, the UHC-member list for a UHC member.</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>The two are not interchangeable. 64772 is absent from the BCBS-member list. The UHC-member list is still unchecked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="68" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>AZPC (Arizona Priority Care)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>INVERTED - lists what does NOT require authorization.</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Not on the list = AUTH IS REQUIRED. Submit through AZ Connect.</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>64772 is not on the 8.21.2026 grid, so auth is required. The grid also excludes anything outside office/home/free-standing facility, and elective outpatient admissions always require auth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="68" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>eviCore (AZ Blue)</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Specialty programs only, by code list.</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>For 64772: NONE of the eviCore program options applies - do not submit there.</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>64772 appears on NO eviCore list: zero 647xx codes on the AZ Blue MSK code list, and CMM-208 covers only 64633-64636 and 64640. If forced to pick a program to get a documented response, choose Musculoskeletal Management and expect 'not managed by eviCore' - screenshot that. Do NOT use 'Other Services'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="68" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>eviCore delegation test</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Some standard-requirement groups are NOT delegated to eviCore.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Check eligibility &amp; benefits, service type 30 (Health Benefit Plan Coverage), look under 'Network Unknown'.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>From AZ Blue's own code-list Introduction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="68" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>AmeriBen (Jointly Administered: K8Y, K8Z, MKQ, PTP and others)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Offers three criteria sets: MCG, HealthLink medical policies, Carelon.</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>For a surgical code start with MCG - ask for the Ambulatory Care (AC) unit AND Inpatient &amp; Surgical Care (ISC).</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>The SPD outranks all three. Carelon's Interventional Pain guideline covers injections and RF ablation, not open neurectomy. HealthLink applies only if that group rents that network. The PRECERT LETTER names the guideline actually used - use it rather than guessing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MCG (Milliman)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Proprietary and licensed - providers cannot browse it.</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>There is no public MCG link for 64772 criteria. Get it from the payer.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Three routes: ask whether MCG criteria are surfaced in Availity (some plans do this); request the guideline title/number in writing; or read the determination letter, which names it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>FEP</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Exception-based medical policies; most routine surgical codes have none.</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Search the FULL policy index, not the monthly update bulletin.</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Keywords: 64772, transection, avulsion, neurectomy, rhizotomy, denervation, peripheral nerve. On the UM page search 'prior approval', not 'prior authorization'. Browse the 7.01.xx surgical block.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Billing BOTH claims - what to confirm before the case</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>We bill the facility (UB-04) and the professional (CMS-1500). One authorization may not protect both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Ask the payer / confirm</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Does ONE authorization cover BOTH the facility and the professional claim, or does the facility need its own?</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Some payers issue a single auth for the service; others require the facility to obtain a separate one. The facility claim denies on its own if not covered.</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Is the authorization tied to a specific TIN / NPI?</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>If it is issued against Dr. Luke's professional NPI only, the FACILITY claim can deny for 'no authorization on file' even though an auth exists.</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Does the authorization name the place of service or the facility?</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>If it does, moving the case to a different site after approval invalidates it.</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Which claim format does this payer want from the ASC - UB-04, or CMS-1500 with POS 24?</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>It varies by payer. The wrong format is a front-end rejection, not a denial.</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Is there a SITE-OF-SERVICE review policy for this code?</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>A site-of-service determination kills the FACILITY claim, not the professional one. The professional side still pays; our facility revenue is what disappears.</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>TO CONFIRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>For AZPC members: is the auth obtained for both claims?</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>AZPC is the one AZ Blue entity requiring prior auth for 64772. Under the July 2026 rule a missed auth is a total write-off and cannot be billed to the member.</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>REQUIRED - see 64772 Determinations</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Medicare note: 64772 has NO non-facility payment (the PFS non-facility PE carries the 'NA' indicator), so POS 11 is unpayable on Medicare. ASC pays $948.66 (Addendum AA, indicator A2); HOPD pays $1,765.76 (APC 5431).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>That 'facility only' finding is a MEDICARE fee-schedule fact. It does not automatically carry to AZ Blue, FEP or a self-funded TPA plan - confirm the office/facility question per payer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare MP.12.22 (Office-Based Procedures - Site of Service) expressly rejects 'surgeon-preferred or proprietary instruments' as grounds for an ASC over an office. If new equipment is the argument for the ASC, UHC has pre-emptively refused it.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2364,7 +2829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
